--- a/scripts/guardian-imports/links/inputs/guardian-links.xlsx
+++ b/scripts/guardian-imports/links/inputs/guardian-links.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\guardian-imports\links\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450E4948-7C58-49F1-A899-9C6FE1A237F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC236FA8-5108-483A-89D2-5964091E01D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="4905" windowWidth="11895" windowHeight="8190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16560" yWindow="3510" windowWidth="10800" windowHeight="6765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="guardian-links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
     <t>active</t>
   </si>
   <si>
-    <t>FATHER</t>
+    <t>MOTHER</t>
   </si>
 </sst>
 </file>
@@ -68,7 +68,6 @@
       <name val="Tajawal"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Tajawal"/>
@@ -407,12 +406,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="19.5" x14ac:dyDescent="0.45">
-      <c r="A2" s="2">
-        <v>1067081024</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1179734650</v>
+    <row r="2" spans="1:4" ht="17.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1093648168</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1200055505</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
